--- a/assests/invoice_template/CHY.xlsx
+++ b/assests/invoice_template/CHY.xlsx
@@ -35,7 +35,7 @@
     <t>申请部门：</t>
   </si>
   <si>
-    <t>生产经营管理部</t>
+    <t>生产经营管理科</t>
   </si>
   <si>
     <t>申请日期：</t>
@@ -147,6 +147,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">专用发票 </t>
     </r>
     <r>
@@ -249,7 +254,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="[DBNum2][$-804]General"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,11 +303,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -461,13 +461,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -943,133 +936,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0">
@@ -1078,11 +1071,11 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1185,10 +1178,7 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="10" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="10" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="11" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="11" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="12" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1197,25 +1187,25 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="3" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="3" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="10" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="10" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1">
@@ -1224,7 +1214,7 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1660,21 +1650,21 @@
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="37"/>
-      <c r="Y4" s="37"/>
-      <c r="Z4" s="37"/>
-      <c r="AA4" s="37"/>
-      <c r="AB4" s="37"/>
-      <c r="AC4" s="37"/>
-      <c r="AD4" s="37"/>
-      <c r="AE4" s="37"/>
-      <c r="AF4" s="37"/>
-      <c r="AG4" s="37"/>
-      <c r="AH4" s="37"/>
-      <c r="AI4" s="37"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
       <c r="AJ4" s="6" t="s">
         <v>3</v>
       </c>
@@ -1682,20 +1672,20 @@
       <c r="AL4" s="6"/>
       <c r="AM4" s="6"/>
       <c r="AN4" s="6"/>
-      <c r="AO4" s="48"/>
-      <c r="AP4" s="48"/>
-      <c r="AQ4" s="49" t="s">
+      <c r="AO4" s="47"/>
+      <c r="AP4" s="47"/>
+      <c r="AQ4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AR4" s="49"/>
-      <c r="AS4" s="49" t="s">
+      <c r="AR4" s="48"/>
+      <c r="AS4" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AT4" s="49"/>
-      <c r="AU4" s="49" t="s">
+      <c r="AT4" s="48"/>
+      <c r="AU4" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AV4" s="37"/>
+      <c r="AV4" s="36"/>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:48">
       <c r="A5" s="4"/>
@@ -1721,105 +1711,105 @@
         <f>IF(ISNUMBER(FIND("¥",AM6)),"零",AM6)</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="38" t="s">
+      <c r="Q5" s="37" t="s">
         <v>9</v>
       </c>
       <c r="R5" s="30">
         <f>IF(ISNUMBER(FIND("¥",AN6)),"零",AN6)</f>
         <v>0</v>
       </c>
-      <c r="S5" s="39" t="s">
+      <c r="S5" s="38" t="s">
         <v>10</v>
       </c>
       <c r="T5" s="30">
         <f>IF(ISNUMBER(FIND("¥",AO6)),"零",AO6)</f>
         <v>0</v>
       </c>
-      <c r="U5" s="39" t="s">
+      <c r="U5" s="38" t="s">
         <v>11</v>
       </c>
       <c r="V5" s="30">
         <f>IF(ISNUMBER(FIND("¥",AP6)),"零",AP6)</f>
         <v>0</v>
       </c>
-      <c r="W5" s="39" t="s">
+      <c r="W5" s="38" t="s">
         <v>12</v>
       </c>
       <c r="X5" s="30">
         <f>IF(ISNUMBER(FIND("¥",AQ6)),"零",AQ6)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="39" t="s">
+      <c r="Y5" s="38" t="s">
         <v>9</v>
       </c>
       <c r="Z5" s="30">
         <f>IF(ISNUMBER(FIND("¥",AR6)),"零",AR6)</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="39" t="s">
+      <c r="AA5" s="38" t="s">
         <v>10</v>
       </c>
       <c r="AB5" s="30">
         <f>IF(ISNUMBER(FIND("¥",AS6)),"零",AS6)</f>
         <v>0</v>
       </c>
-      <c r="AC5" s="39" t="s">
+      <c r="AC5" s="38" t="s">
         <v>11</v>
       </c>
       <c r="AD5" s="30">
         <f>IF(ISNUMBER(FIND("¥",AT6)),"零",AT6)</f>
         <v>0</v>
       </c>
-      <c r="AE5" s="39" t="s">
+      <c r="AE5" s="38" t="s">
         <v>13</v>
       </c>
       <c r="AF5" s="30">
         <f>IF(ISNUMBER(FIND("¥",AU6)),"零",AU6)</f>
         <v>0</v>
       </c>
-      <c r="AG5" s="39" t="s">
+      <c r="AG5" s="38" t="s">
         <v>14</v>
       </c>
       <c r="AH5" s="30">
         <f>IF(ISNUMBER(FIND("¥",AV6)),"零",AV6)</f>
         <v>0</v>
       </c>
-      <c r="AI5" s="41" t="s">
+      <c r="AI5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="AJ5" s="42" t="s">
+      <c r="AJ5" s="41" t="s">
         <v>16</v>
       </c>
       <c r="AK5" s="29"/>
       <c r="AL5" s="29"/>
-      <c r="AM5" s="43" t="s">
+      <c r="AM5" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="AN5" s="44" t="s">
+      <c r="AN5" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="AO5" s="43" t="s">
+      <c r="AO5" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="AP5" s="43" t="s">
+      <c r="AP5" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="43" t="s">
+      <c r="AQ5" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="43" t="s">
+      <c r="AR5" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="43" t="s">
+      <c r="AS5" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="43" t="s">
+      <c r="AT5" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AU5" s="43" t="s">
+      <c r="AU5" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="AV5" s="43" t="s">
+      <c r="AV5" s="42" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1840,38 +1830,38 @@
       <c r="N6" s="31"/>
       <c r="O6" s="31"/>
       <c r="P6" s="32"/>
-      <c r="Q6" s="40"/>
+      <c r="Q6" s="39"/>
       <c r="R6" s="32"/>
-      <c r="S6" s="40"/>
+      <c r="S6" s="39"/>
       <c r="T6" s="32"/>
-      <c r="U6" s="40"/>
+      <c r="U6" s="39"/>
       <c r="V6" s="32"/>
-      <c r="W6" s="40"/>
+      <c r="W6" s="39"/>
       <c r="X6" s="32"/>
-      <c r="Y6" s="40"/>
+      <c r="Y6" s="39"/>
       <c r="Z6" s="32"/>
-      <c r="AA6" s="40"/>
+      <c r="AA6" s="39"/>
       <c r="AB6" s="32"/>
-      <c r="AC6" s="40"/>
+      <c r="AC6" s="39"/>
       <c r="AD6" s="32"/>
-      <c r="AE6" s="40"/>
+      <c r="AE6" s="39"/>
       <c r="AF6" s="32"/>
-      <c r="AG6" s="40"/>
+      <c r="AG6" s="39"/>
       <c r="AH6" s="32"/>
-      <c r="AI6" s="45"/>
-      <c r="AJ6" s="46"/>
+      <c r="AI6" s="44"/>
+      <c r="AJ6" s="45"/>
       <c r="AK6" s="31"/>
       <c r="AL6" s="31"/>
-      <c r="AM6" s="47"/>
-      <c r="AN6" s="47"/>
-      <c r="AO6" s="47"/>
-      <c r="AP6" s="47"/>
-      <c r="AQ6" s="47"/>
-      <c r="AR6" s="47"/>
-      <c r="AS6" s="47"/>
-      <c r="AT6" s="47"/>
-      <c r="AU6" s="47"/>
-      <c r="AV6" s="47"/>
+      <c r="AM6" s="46"/>
+      <c r="AN6" s="46"/>
+      <c r="AO6" s="46"/>
+      <c r="AP6" s="46"/>
+      <c r="AQ6" s="46"/>
+      <c r="AR6" s="46"/>
+      <c r="AS6" s="46"/>
+      <c r="AT6" s="46"/>
+      <c r="AU6" s="46"/>
+      <c r="AV6" s="46"/>
     </row>
     <row r="7" ht="37.5" customHeight="1" spans="1:48">
       <c r="A7" s="13"/>
@@ -1947,7 +1937,7 @@
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
-      <c r="N8" s="34"/>
+      <c r="N8" s="20"/>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
       <c r="Q8" s="20"/>
@@ -2220,48 +2210,48 @@
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
       <c r="H13" s="23"/>
-      <c r="I13" s="35" t="s">
+      <c r="I13" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36"/>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="36"/>
-      <c r="AC13" s="36"/>
-      <c r="AD13" s="36"/>
-      <c r="AE13" s="36"/>
-      <c r="AF13" s="36"/>
-      <c r="AG13" s="36"/>
-      <c r="AH13" s="36"/>
-      <c r="AI13" s="36"/>
-      <c r="AJ13" s="36"/>
-      <c r="AK13" s="36"/>
-      <c r="AL13" s="36"/>
-      <c r="AM13" s="36"/>
-      <c r="AN13" s="36"/>
-      <c r="AO13" s="36"/>
-      <c r="AP13" s="36"/>
-      <c r="AQ13" s="36"/>
-      <c r="AR13" s="36"/>
-      <c r="AS13" s="36"/>
-      <c r="AT13" s="36"/>
-      <c r="AU13" s="36"/>
-      <c r="AV13" s="50"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="35"/>
+      <c r="AC13" s="35"/>
+      <c r="AD13" s="35"/>
+      <c r="AE13" s="35"/>
+      <c r="AF13" s="35"/>
+      <c r="AG13" s="35"/>
+      <c r="AH13" s="35"/>
+      <c r="AI13" s="35"/>
+      <c r="AJ13" s="35"/>
+      <c r="AK13" s="35"/>
+      <c r="AL13" s="35"/>
+      <c r="AM13" s="35"/>
+      <c r="AN13" s="35"/>
+      <c r="AO13" s="35"/>
+      <c r="AP13" s="35"/>
+      <c r="AQ13" s="35"/>
+      <c r="AR13" s="35"/>
+      <c r="AS13" s="35"/>
+      <c r="AT13" s="35"/>
+      <c r="AU13" s="35"/>
+      <c r="AV13" s="49"/>
     </row>
     <row r="14" ht="37.5" customHeight="1" spans="1:48">
       <c r="A14" s="4"/>

--- a/assests/invoice_template/CHY.xlsx
+++ b/assests/invoice_template/CHY.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="30720" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="开票申请单（测绘院） (3)" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <t>申请部门：</t>
   </si>
   <si>
-    <t>生产经营管理科</t>
+    <t>生产经营管理部</t>
   </si>
   <si>
     <t>申请日期：</t>
@@ -1910,14 +1910,14 @@
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
       <c r="AN7" s="20"/>
-      <c r="AO7" s="20"/>
-      <c r="AP7" s="20"/>
-      <c r="AQ7" s="20"/>
-      <c r="AR7" s="20"/>
-      <c r="AS7" s="20"/>
-      <c r="AT7" s="20"/>
-      <c r="AU7" s="20"/>
-      <c r="AV7" s="20"/>
+      <c r="AO7" s="33"/>
+      <c r="AP7" s="33"/>
+      <c r="AQ7" s="33"/>
+      <c r="AR7" s="33"/>
+      <c r="AS7" s="33"/>
+      <c r="AT7" s="33"/>
+      <c r="AU7" s="33"/>
+      <c r="AV7" s="33"/>
     </row>
     <row r="8" ht="37.5" customHeight="1" spans="1:48">
       <c r="A8" s="13"/>
@@ -1937,28 +1937,28 @@
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20"/>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="20"/>
-      <c r="AE8" s="20"/>
-      <c r="AF8" s="20"/>
-      <c r="AG8" s="20"/>
-      <c r="AH8" s="20"/>
-      <c r="AI8" s="20"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="33"/>
+      <c r="AC8" s="33"/>
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="33"/>
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="33"/>
       <c r="AJ8" s="20" t="s">
         <v>25</v>
       </c>
@@ -1966,14 +1966,14 @@
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
       <c r="AN8" s="20"/>
-      <c r="AO8" s="20"/>
-      <c r="AP8" s="20"/>
-      <c r="AQ8" s="20"/>
-      <c r="AR8" s="20"/>
-      <c r="AS8" s="20"/>
-      <c r="AT8" s="20"/>
-      <c r="AU8" s="20"/>
-      <c r="AV8" s="20"/>
+      <c r="AO8" s="33"/>
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="33"/>
+      <c r="AR8" s="33"/>
+      <c r="AS8" s="33"/>
+      <c r="AT8" s="33"/>
+      <c r="AU8" s="33"/>
+      <c r="AV8" s="33"/>
     </row>
     <row r="9" ht="37.5" customHeight="1" spans="1:48">
       <c r="A9" s="13"/>
@@ -2026,14 +2026,14 @@
       <c r="AL9" s="25"/>
       <c r="AM9" s="25"/>
       <c r="AN9" s="26"/>
-      <c r="AO9" s="24"/>
-      <c r="AP9" s="25"/>
-      <c r="AQ9" s="25"/>
-      <c r="AR9" s="25"/>
-      <c r="AS9" s="25"/>
-      <c r="AT9" s="25"/>
-      <c r="AU9" s="25"/>
-      <c r="AV9" s="26"/>
+      <c r="AO9" s="21"/>
+      <c r="AP9" s="22"/>
+      <c r="AQ9" s="22"/>
+      <c r="AR9" s="22"/>
+      <c r="AS9" s="22"/>
+      <c r="AT9" s="22"/>
+      <c r="AU9" s="22"/>
+      <c r="AV9" s="23"/>
     </row>
     <row r="10" ht="37.5" customHeight="1" spans="1:48">
       <c r="A10" s="4"/>
@@ -2053,28 +2053,28 @@
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
       <c r="M10" s="20"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="25"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="25"/>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="25"/>
-      <c r="AE10" s="25"/>
-      <c r="AF10" s="25"/>
-      <c r="AG10" s="25"/>
-      <c r="AH10" s="25"/>
-      <c r="AI10" s="26"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="22"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
+      <c r="AE10" s="22"/>
+      <c r="AF10" s="22"/>
+      <c r="AG10" s="22"/>
+      <c r="AH10" s="22"/>
+      <c r="AI10" s="23"/>
       <c r="AJ10" s="20" t="s">
         <v>33</v>
       </c>
@@ -2082,14 +2082,14 @@
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
       <c r="AN10" s="20"/>
-      <c r="AO10" s="24"/>
-      <c r="AP10" s="25"/>
-      <c r="AQ10" s="25"/>
-      <c r="AR10" s="25"/>
-      <c r="AS10" s="25"/>
-      <c r="AT10" s="25"/>
-      <c r="AU10" s="25"/>
-      <c r="AV10" s="26"/>
+      <c r="AO10" s="21"/>
+      <c r="AP10" s="22"/>
+      <c r="AQ10" s="22"/>
+      <c r="AR10" s="22"/>
+      <c r="AS10" s="22"/>
+      <c r="AT10" s="22"/>
+      <c r="AU10" s="22"/>
+      <c r="AV10" s="23"/>
     </row>
     <row r="11" ht="37.5" customHeight="1" spans="1:48">
       <c r="A11" s="4"/>
@@ -2107,28 +2107,28 @@
       <c r="K11" s="20"/>
       <c r="L11" s="20"/>
       <c r="M11" s="20"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
-      <c r="AH11" s="25"/>
-      <c r="AI11" s="26"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="22"/>
+      <c r="AF11" s="22"/>
+      <c r="AG11" s="22"/>
+      <c r="AH11" s="22"/>
+      <c r="AI11" s="23"/>
       <c r="AJ11" s="20" t="s">
         <v>35</v>
       </c>
@@ -2136,14 +2136,14 @@
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
       <c r="AN11" s="20"/>
-      <c r="AO11" s="24"/>
-      <c r="AP11" s="25"/>
-      <c r="AQ11" s="25"/>
-      <c r="AR11" s="25"/>
-      <c r="AS11" s="25"/>
-      <c r="AT11" s="25"/>
-      <c r="AU11" s="25"/>
-      <c r="AV11" s="26"/>
+      <c r="AO11" s="21"/>
+      <c r="AP11" s="22"/>
+      <c r="AQ11" s="22"/>
+      <c r="AR11" s="22"/>
+      <c r="AS11" s="22"/>
+      <c r="AT11" s="22"/>
+      <c r="AU11" s="22"/>
+      <c r="AV11" s="23"/>
     </row>
     <row r="12" ht="37.5" customHeight="1" spans="1:48">
       <c r="A12" s="4"/>
@@ -2161,28 +2161,28 @@
       <c r="K12" s="20"/>
       <c r="L12" s="20"/>
       <c r="M12" s="20"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
-      <c r="X12" s="25"/>
-      <c r="Y12" s="25"/>
-      <c r="Z12" s="25"/>
-      <c r="AA12" s="25"/>
-      <c r="AB12" s="25"/>
-      <c r="AC12" s="25"/>
-      <c r="AD12" s="25"/>
-      <c r="AE12" s="25"/>
-      <c r="AF12" s="25"/>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="25"/>
-      <c r="AI12" s="26"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="22"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
+      <c r="AE12" s="22"/>
+      <c r="AF12" s="22"/>
+      <c r="AG12" s="22"/>
+      <c r="AH12" s="22"/>
+      <c r="AI12" s="23"/>
       <c r="AJ12" s="20" t="s">
         <v>37</v>
       </c>
@@ -2190,14 +2190,14 @@
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
       <c r="AN12" s="20"/>
-      <c r="AO12" s="24"/>
-      <c r="AP12" s="25"/>
-      <c r="AQ12" s="25"/>
-      <c r="AR12" s="25"/>
-      <c r="AS12" s="25"/>
-      <c r="AT12" s="25"/>
-      <c r="AU12" s="25"/>
-      <c r="AV12" s="26"/>
+      <c r="AO12" s="21"/>
+      <c r="AP12" s="22"/>
+      <c r="AQ12" s="22"/>
+      <c r="AR12" s="22"/>
+      <c r="AS12" s="22"/>
+      <c r="AT12" s="22"/>
+      <c r="AU12" s="22"/>
+      <c r="AV12" s="23"/>
     </row>
     <row r="13" ht="37.5" customHeight="1" spans="1:48">
       <c r="A13" s="13"/>
